--- a/Streamlit.xlsx
+++ b/Streamlit.xlsx
@@ -11,12 +11,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="113">
   <si>
     <t>name</t>
   </si>
   <si>
-    <t>type</t>
+    <t>Categories</t>
   </si>
   <si>
     <t>engagament</t>
@@ -25,10 +25,10 @@
     <t>color</t>
   </si>
   <si>
-    <t>relationship</t>
-  </si>
-  <si>
-    <t>Expertise</t>
+    <t>Expertise Areas</t>
+  </si>
+  <si>
+    <t>Engagement Summary</t>
   </si>
   <si>
     <t>AWC</t>
@@ -40,37 +40,55 @@
     <t>red</t>
   </si>
   <si>
-    <t>partnered with</t>
-  </si>
-  <si>
-    <t>AI, VR, War Game</t>
+    <t>AI &amp; Data; Education &amp; PME; Futures &amp; Strategy</t>
+  </si>
+  <si>
+    <t>Used Project SE-OA to review AWC curriculum for joint-warfighting and lethality alignment. Also supported Alpha Blue and AI-enabled reading, writing, and research.</t>
   </si>
   <si>
     <t>ACSC</t>
   </si>
   <si>
-    <t>Robotics</t>
+    <t>AI &amp; Data; Education &amp; PME; Wargaming; Fabrication &amp; sUAS; Innovation &amp; Design</t>
+  </si>
+  <si>
+    <t>Partnered on AI study skills, Project CHUCK, Project DRADIS, Praxeum, wargame maps, Alpha Blue research, and sUAS prototypes including Centurion, Killer Robots, and Maple Seed.</t>
   </si>
   <si>
     <t>SOS</t>
   </si>
   <si>
-    <t>VR</t>
+    <t>Education &amp; PME; Wargaming; Innovation &amp; Design</t>
+  </si>
+  <si>
+    <t>Supported AFWI/Project CHUCK, Praxeum, AUAR research, Echo Lab wargame materials, AI 101, and LEGO Serious Play instruction.</t>
   </si>
   <si>
     <t>Lemay</t>
   </si>
   <si>
+    <t>Wargaming; AI &amp; Data; Education &amp; PME</t>
+  </si>
+  <si>
+    <t>Requested and supported Project CHUCK, joint-planning applications, Power BI training, wargame materials, and sUAS work.</t>
+  </si>
+  <si>
     <t>AFIT</t>
   </si>
   <si>
-    <t>PME</t>
+    <t>Education &amp; PME; Innovation &amp; Design; AI &amp; Data</t>
+  </si>
+  <si>
+    <t>Supported Education With Industry fellows and coaches through solution framing, double-diamond design, LEGO Serious Play, and AI-enabled problem solving.</t>
   </si>
   <si>
     <t>Barnes</t>
   </si>
   <si>
-    <t>Research</t>
+    <t>Education &amp; PME; AI &amp; Data; Wargaming</t>
+  </si>
+  <si>
+    <t>Received AI literacy and curriculum-development training and collaborated on Project CHUCK, Kingfish ACE, learning objectives, KPIs, and SBIR exploration.</t>
   </si>
   <si>
     <t>AFGC</t>
@@ -82,21 +100,33 @@
     <t>AU HQ</t>
   </si>
   <si>
-    <t>AI, VR, War Game, Robotics, Research</t>
+    <t>AI &amp; Data; Education &amp; PME; Policy &amp; Acquisition</t>
+  </si>
+  <si>
+    <t>Participated in AI 101, Power BI, VECTOR/Beacon faculty development, Praxeum, and cross-AU AI policy roundtables.</t>
   </si>
   <si>
     <t>Eaker Center</t>
   </si>
   <si>
-    <t>3D Printing</t>
+    <t>Partnered on Power BI instruction and Wing Chaplain Course support using LEGO Serious Play and problem-framing methods.</t>
   </si>
   <si>
     <t>MSFRIC</t>
   </si>
   <si>
+    <t>AI &amp; Data; Software &amp; Automation; Education &amp; PME</t>
+  </si>
+  <si>
+    <t>Partnered on CODEX DROID, a custom GPT for the AU Style Guide, article taxonomy, indexing, and publishing workflows.</t>
+  </si>
+  <si>
     <t>IOS</t>
   </si>
   <si>
+    <t>Integrated the Eagle Institute into AY26 onboarding to expose international officers to innovation, AI, and wargaming.</t>
+  </si>
+  <si>
     <t>SAASS</t>
   </si>
   <si>
@@ -109,30 +139,72 @@
     <t>Blue</t>
   </si>
   <si>
+    <t>AI &amp; Data; Human Performance; Community &amp; Workforce; Education &amp; PME</t>
+  </si>
+  <si>
+    <t>Collaborated through the Biggio Center, Warrior Research Center, GearUP/PELLA, course redesign, and Invention Convention Alabama.</t>
+  </si>
+  <si>
     <t>MPS</t>
   </si>
   <si>
+    <t>Community &amp; Workforce; Education &amp; PME</t>
+  </si>
+  <si>
+    <t>Partnered on a Goodwyn Middle School STEM Café session featuring robotics, drones, AR/VR, and 3D printing.</t>
+  </si>
+  <si>
     <t>MIT</t>
   </si>
   <si>
+    <t>AI &amp; Data; Education &amp; PME; Innovation &amp; Design</t>
+  </si>
+  <si>
+    <t>Supported the Air Power U Summer Workshop Series on AI for research, curriculum, and learning-space design.</t>
+  </si>
+  <si>
     <t>Troy</t>
   </si>
   <si>
+    <t>AI &amp; Data; Software &amp; Automation; Fabrication &amp; sUAS; Innovation &amp; Design</t>
+  </si>
+  <si>
+    <t>Provided faculty and intern support for AI workshops, ACSC hackathons, Project ATLAS, and acoustic drone-detection research.</t>
+  </si>
+  <si>
     <t>ASU</t>
   </si>
   <si>
     <t>Stanford</t>
   </si>
   <si>
+    <t>Partnered on Phoenix Dialogue through the Deliberative Democracy Lab and supported internships focused on AI in PME.</t>
+  </si>
+  <si>
     <t>AUM</t>
   </si>
   <si>
+    <t>Software &amp; Automation; Fabrication &amp; sUAS; Innovation &amp; Design; Community &amp; Workforce</t>
+  </si>
+  <si>
+    <t>Collaborated on ACSC hackathons, Project Killer Robots, internships, and prototyping support.</t>
+  </si>
+  <si>
     <t>William &amp; Mary</t>
   </si>
   <si>
+    <t>AI &amp; Data; Wargaming; Education &amp; PME</t>
+  </si>
+  <si>
+    <t>An intern supported further Project CHUCK testing at USAFA for Operation Northern Eclipse.</t>
+  </si>
+  <si>
     <t>Treholm</t>
   </si>
   <si>
+    <t>Identified as an internship partner. No specific project outcome was provided.</t>
+  </si>
+  <si>
     <t>Invoke Public Sector</t>
   </si>
   <si>
@@ -142,9 +214,21 @@
     <t>Yellow</t>
   </si>
   <si>
+    <t>Software &amp; Automation; AI &amp; Data</t>
+  </si>
+  <si>
+    <t>Partnered on robotic process automation, workflow automation, and commercial AI training.</t>
+  </si>
+  <si>
     <t>MGM Tech Lab</t>
   </si>
   <si>
+    <t>Policy &amp; Acquisition; Innovation &amp; Design; Community &amp; Workforce</t>
+  </si>
+  <si>
+    <t>Supported Defense Accelerator Demo Day, connecting businesses with defense SMEs on critical technologies and acquisition processes.</t>
+  </si>
+  <si>
     <t>Aptima</t>
   </si>
   <si>
@@ -163,18 +247,42 @@
     <t xml:space="preserve"> Deloitte</t>
   </si>
   <si>
+    <t>AI &amp; Data; Policy &amp; Acquisition</t>
+  </si>
+  <si>
+    <t>Connected during the Alabama Higher Education AI Exchange to discuss AI integration, academic integrity, and cross-sector adoption.</t>
+  </si>
+  <si>
     <t>HII</t>
   </si>
   <si>
     <t>AWS</t>
   </si>
   <si>
+    <t>AI &amp; Data; Wargaming; Software &amp; Automation</t>
+  </si>
+  <si>
+    <t>Expressed interest in supporting a prototype AI-driven wargame.</t>
+  </si>
+  <si>
     <t>OMNI Federal</t>
   </si>
   <si>
+    <t>Futures &amp; Strategy; Education &amp; PME; Software &amp; Automation</t>
+  </si>
+  <si>
+    <t>Built and demonstrated a Futures Literacy virtual mini-course prototype under a CRADA; Johns Hopkins agreed to design the curriculum.</t>
+  </si>
+  <si>
     <t>Coca Cola</t>
   </si>
   <si>
+    <t>Education &amp; PME</t>
+  </si>
+  <si>
+    <t>Listed as a partner for curriculum and specialized-topic programming.</t>
+  </si>
+  <si>
     <t>SBIR Advisor</t>
   </si>
   <si>
@@ -196,6 +304,9 @@
     <t>BESPIN</t>
   </si>
   <si>
+    <t>Software &amp; Automation; Education &amp; PME</t>
+  </si>
+  <si>
     <t>HAF5/7</t>
   </si>
   <si>
@@ -206,13 +317,46 @@
   </si>
   <si>
     <t>Army War College</t>
+  </si>
+  <si>
+    <t>Education &amp; PME; AI &amp; Data</t>
+  </si>
+  <si>
+    <t>Participated in cross-service collaboration on AI adoption in professional military education.</t>
+  </si>
+  <si>
+    <t>AI &amp; Data</t>
+  </si>
+  <si>
+    <t>Wargaming</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Futures &amp; Strategy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innovation &amp; Design </t>
+  </si>
+  <si>
+    <t>Software &amp; Automation</t>
+  </si>
+  <si>
+    <t>Fabrication &amp; sUAS</t>
+  </si>
+  <si>
+    <t>Human Performance</t>
+  </si>
+  <si>
+    <t>Policy &amp; Acquisition</t>
+  </si>
+  <si>
+    <t>Community &amp; Workforce.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -223,6 +367,10 @@
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="11.0"/>
@@ -250,14 +398,20 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="top"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -478,6 +632,8 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="25.38"/>
+    <col customWidth="1" min="5" max="5" width="72.0"/>
+    <col customWidth="1" min="6" max="6" width="150.0"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -493,10 +649,10 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
@@ -513,10 +669,10 @@
       <c r="D2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>10</v>
       </c>
     </row>
@@ -533,16 +689,16 @@
       <c r="D3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>12</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -553,16 +709,16 @@
       <c r="D4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>14</v>
+      <c r="E4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
@@ -573,16 +729,16 @@
       <c r="D5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>10</v>
+      <c r="E5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
@@ -593,16 +749,16 @@
       <c r="D6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>17</v>
+      <c r="E6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
@@ -613,16 +769,16 @@
       <c r="D7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>19</v>
+      <c r="E7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
@@ -633,16 +789,12 @@
       <c r="D8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>19</v>
-      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
@@ -653,16 +805,12 @@
       <c r="D9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>10</v>
-      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
@@ -673,16 +821,16 @@
       <c r="D10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>23</v>
+      <c r="E10" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
@@ -693,16 +841,16 @@
       <c r="D11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>25</v>
+      <c r="E11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
@@ -713,16 +861,16 @@
       <c r="D12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>10</v>
+      <c r="E12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
@@ -733,16 +881,16 @@
       <c r="D13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>12</v>
+      <c r="E13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
@@ -753,611 +901,601 @@
       <c r="D14" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>14</v>
-      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C15" s="1">
         <v>10.0</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>10</v>
+        <v>41</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C16" s="1">
         <v>1.0</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>17</v>
+        <v>41</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C17" s="1">
         <v>3.0</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>19</v>
+        <v>41</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C18" s="1">
         <v>7.0</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>19</v>
+        <v>41</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C19" s="1">
         <v>2.0</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>10</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C20" s="1">
         <v>5.0</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>23</v>
+        <v>41</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C21" s="1">
         <v>6.0</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>12</v>
+        <v>41</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C22" s="1">
         <v>2.0</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>14</v>
+        <v>41</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C23" s="1">
         <v>4.0</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>10</v>
+        <v>41</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="C24" s="1">
         <v>2.0</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>10</v>
+        <v>66</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="C25" s="1">
         <v>5.0</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>12</v>
+        <v>66</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="C26" s="1">
         <v>2.0</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>14</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="C27" s="1">
         <v>2.0</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>10</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="C28" s="1">
         <v>2.0</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>17</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="s">
-        <v>47</v>
+      <c r="A29" s="4" t="s">
+        <v>75</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="C29" s="1">
         <v>2.0</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>19</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="s">
-        <v>48</v>
+      <c r="A30" s="4" t="s">
+        <v>76</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="C30" s="1">
         <v>2.0</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>19</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="C31" s="1">
         <v>2.0</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>10</v>
+        <v>66</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="C32" s="1">
         <v>11.0</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>23</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="C33" s="1">
         <v>8.0</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>17</v>
+        <v>66</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>52</v>
+        <v>84</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="C34" s="1">
         <v>6.0</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>19</v>
+        <v>66</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="C35" s="1">
         <v>6.0</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>19</v>
+        <v>66</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="C36" s="1">
         <v>6.0</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>10</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="s">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="C37" s="1">
         <v>1.0</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>23</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="s">
-        <v>56</v>
+        <v>92</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="C38" s="1">
         <v>1.0</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>25</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
     </row>
     <row r="39">
       <c r="A39" s="1" t="s">
-        <v>59</v>
+        <v>95</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="C39" s="1">
         <v>9.0</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>10</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
     </row>
     <row r="40">
       <c r="A40" s="1" t="s">
-        <v>60</v>
+        <v>96</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="C40" s="1">
         <v>8.0</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>12</v>
+        <v>94</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="C41" s="1">
         <v>6.0</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>14</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
     </row>
     <row r="42">
       <c r="A42" s="1" t="s">
-        <v>62</v>
+        <v>99</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="C42" s="1">
         <v>2.0</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>10</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
     </row>
     <row r="43">
       <c r="A43" s="1" t="s">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="C43" s="1">
         <v>2.0</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>12</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
     </row>
     <row r="44">
       <c r="A44" s="1" t="s">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="C44" s="1">
         <v>2.0</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>14</v>
+        <v>94</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="E47" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="E48" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="E49" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="E50" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="E51" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="E52" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="E53" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="E54" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="E55" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="E56" s="1" t="s">
+        <v>112</v>
       </c>
     </row>
   </sheetData>

--- a/Streamlit.xlsx
+++ b/Streamlit.xlsx
@@ -11,12 +11,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="65">
   <si>
     <t>name</t>
   </si>
   <si>
-    <t>Categories</t>
+    <t>type</t>
   </si>
   <si>
     <t>engagament</t>
@@ -25,10 +25,10 @@
     <t>color</t>
   </si>
   <si>
-    <t>Expertise Areas</t>
-  </si>
-  <si>
-    <t>Engagement Summary</t>
+    <t>relationship</t>
+  </si>
+  <si>
+    <t>Expertise</t>
   </si>
   <si>
     <t>AWC</t>
@@ -40,55 +40,37 @@
     <t>red</t>
   </si>
   <si>
-    <t>AI &amp; Data; Education &amp; PME; Futures &amp; Strategy</t>
-  </si>
-  <si>
-    <t>Used Project SE-OA to review AWC curriculum for joint-warfighting and lethality alignment. Also supported Alpha Blue and AI-enabled reading, writing, and research.</t>
+    <t>partnered with</t>
+  </si>
+  <si>
+    <t>AI, VR, War Game</t>
   </si>
   <si>
     <t>ACSC</t>
   </si>
   <si>
-    <t>AI &amp; Data; Education &amp; PME; Wargaming; Fabrication &amp; sUAS; Innovation &amp; Design</t>
-  </si>
-  <si>
-    <t>Partnered on AI study skills, Project CHUCK, Project DRADIS, Praxeum, wargame maps, Alpha Blue research, and sUAS prototypes including Centurion, Killer Robots, and Maple Seed.</t>
+    <t>Robotics</t>
   </si>
   <si>
     <t>SOS</t>
   </si>
   <si>
-    <t>Education &amp; PME; Wargaming; Innovation &amp; Design</t>
-  </si>
-  <si>
-    <t>Supported AFWI/Project CHUCK, Praxeum, AUAR research, Echo Lab wargame materials, AI 101, and LEGO Serious Play instruction.</t>
+    <t>VR</t>
   </si>
   <si>
     <t>Lemay</t>
   </si>
   <si>
-    <t>Wargaming; AI &amp; Data; Education &amp; PME</t>
-  </si>
-  <si>
-    <t>Requested and supported Project CHUCK, joint-planning applications, Power BI training, wargame materials, and sUAS work.</t>
-  </si>
-  <si>
     <t>AFIT</t>
   </si>
   <si>
-    <t>Education &amp; PME; Innovation &amp; Design; AI &amp; Data</t>
-  </si>
-  <si>
-    <t>Supported Education With Industry fellows and coaches through solution framing, double-diamond design, LEGO Serious Play, and AI-enabled problem solving.</t>
+    <t>PME</t>
   </si>
   <si>
     <t>Barnes</t>
   </si>
   <si>
-    <t>Education &amp; PME; AI &amp; Data; Wargaming</t>
-  </si>
-  <si>
-    <t>Received AI literacy and curriculum-development training and collaborated on Project CHUCK, Kingfish ACE, learning objectives, KPIs, and SBIR exploration.</t>
+    <t>Research</t>
   </si>
   <si>
     <t>AFGC</t>
@@ -100,33 +82,21 @@
     <t>AU HQ</t>
   </si>
   <si>
-    <t>AI &amp; Data; Education &amp; PME; Policy &amp; Acquisition</t>
-  </si>
-  <si>
-    <t>Participated in AI 101, Power BI, VECTOR/Beacon faculty development, Praxeum, and cross-AU AI policy roundtables.</t>
+    <t>AI, VR, War Game, Robotics, Research</t>
   </si>
   <si>
     <t>Eaker Center</t>
   </si>
   <si>
-    <t>Partnered on Power BI instruction and Wing Chaplain Course support using LEGO Serious Play and problem-framing methods.</t>
+    <t>3D Printing</t>
   </si>
   <si>
     <t>MSFRIC</t>
   </si>
   <si>
-    <t>AI &amp; Data; Software &amp; Automation; Education &amp; PME</t>
-  </si>
-  <si>
-    <t>Partnered on CODEX DROID, a custom GPT for the AU Style Guide, article taxonomy, indexing, and publishing workflows.</t>
-  </si>
-  <si>
     <t>IOS</t>
   </si>
   <si>
-    <t>Integrated the Eagle Institute into AY26 onboarding to expose international officers to innovation, AI, and wargaming.</t>
-  </si>
-  <si>
     <t>SAASS</t>
   </si>
   <si>
@@ -139,72 +109,30 @@
     <t>Blue</t>
   </si>
   <si>
-    <t>AI &amp; Data; Human Performance; Community &amp; Workforce; Education &amp; PME</t>
-  </si>
-  <si>
-    <t>Collaborated through the Biggio Center, Warrior Research Center, GearUP/PELLA, course redesign, and Invention Convention Alabama.</t>
-  </si>
-  <si>
     <t>MPS</t>
   </si>
   <si>
-    <t>Community &amp; Workforce; Education &amp; PME</t>
-  </si>
-  <si>
-    <t>Partnered on a Goodwyn Middle School STEM Café session featuring robotics, drones, AR/VR, and 3D printing.</t>
-  </si>
-  <si>
     <t>MIT</t>
   </si>
   <si>
-    <t>AI &amp; Data; Education &amp; PME; Innovation &amp; Design</t>
-  </si>
-  <si>
-    <t>Supported the Air Power U Summer Workshop Series on AI for research, curriculum, and learning-space design.</t>
-  </si>
-  <si>
     <t>Troy</t>
   </si>
   <si>
-    <t>AI &amp; Data; Software &amp; Automation; Fabrication &amp; sUAS; Innovation &amp; Design</t>
-  </si>
-  <si>
-    <t>Provided faculty and intern support for AI workshops, ACSC hackathons, Project ATLAS, and acoustic drone-detection research.</t>
-  </si>
-  <si>
     <t>ASU</t>
   </si>
   <si>
     <t>Stanford</t>
   </si>
   <si>
-    <t>Partnered on Phoenix Dialogue through the Deliberative Democracy Lab and supported internships focused on AI in PME.</t>
-  </si>
-  <si>
     <t>AUM</t>
   </si>
   <si>
-    <t>Software &amp; Automation; Fabrication &amp; sUAS; Innovation &amp; Design; Community &amp; Workforce</t>
-  </si>
-  <si>
-    <t>Collaborated on ACSC hackathons, Project Killer Robots, internships, and prototyping support.</t>
-  </si>
-  <si>
     <t>William &amp; Mary</t>
   </si>
   <si>
-    <t>AI &amp; Data; Wargaming; Education &amp; PME</t>
-  </si>
-  <si>
-    <t>An intern supported further Project CHUCK testing at USAFA for Operation Northern Eclipse.</t>
-  </si>
-  <si>
     <t>Treholm</t>
   </si>
   <si>
-    <t>Identified as an internship partner. No specific project outcome was provided.</t>
-  </si>
-  <si>
     <t>Invoke Public Sector</t>
   </si>
   <si>
@@ -214,21 +142,9 @@
     <t>Yellow</t>
   </si>
   <si>
-    <t>Software &amp; Automation; AI &amp; Data</t>
-  </si>
-  <si>
-    <t>Partnered on robotic process automation, workflow automation, and commercial AI training.</t>
-  </si>
-  <si>
     <t>MGM Tech Lab</t>
   </si>
   <si>
-    <t>Policy &amp; Acquisition; Innovation &amp; Design; Community &amp; Workforce</t>
-  </si>
-  <si>
-    <t>Supported Defense Accelerator Demo Day, connecting businesses with defense SMEs on critical technologies and acquisition processes.</t>
-  </si>
-  <si>
     <t>Aptima</t>
   </si>
   <si>
@@ -247,42 +163,18 @@
     <t xml:space="preserve"> Deloitte</t>
   </si>
   <si>
-    <t>AI &amp; Data; Policy &amp; Acquisition</t>
-  </si>
-  <si>
-    <t>Connected during the Alabama Higher Education AI Exchange to discuss AI integration, academic integrity, and cross-sector adoption.</t>
-  </si>
-  <si>
     <t>HII</t>
   </si>
   <si>
     <t>AWS</t>
   </si>
   <si>
-    <t>AI &amp; Data; Wargaming; Software &amp; Automation</t>
-  </si>
-  <si>
-    <t>Expressed interest in supporting a prototype AI-driven wargame.</t>
-  </si>
-  <si>
     <t>OMNI Federal</t>
   </si>
   <si>
-    <t>Futures &amp; Strategy; Education &amp; PME; Software &amp; Automation</t>
-  </si>
-  <si>
-    <t>Built and demonstrated a Futures Literacy virtual mini-course prototype under a CRADA; Johns Hopkins agreed to design the curriculum.</t>
-  </si>
-  <si>
     <t>Coca Cola</t>
   </si>
   <si>
-    <t>Education &amp; PME</t>
-  </si>
-  <si>
-    <t>Listed as a partner for curriculum and specialized-topic programming.</t>
-  </si>
-  <si>
     <t>SBIR Advisor</t>
   </si>
   <si>
@@ -304,9 +196,6 @@
     <t>BESPIN</t>
   </si>
   <si>
-    <t>Software &amp; Automation; Education &amp; PME</t>
-  </si>
-  <si>
     <t>HAF5/7</t>
   </si>
   <si>
@@ -317,46 +206,13 @@
   </si>
   <si>
     <t>Army War College</t>
-  </si>
-  <si>
-    <t>Education &amp; PME; AI &amp; Data</t>
-  </si>
-  <si>
-    <t>Participated in cross-service collaboration on AI adoption in professional military education.</t>
-  </si>
-  <si>
-    <t>AI &amp; Data</t>
-  </si>
-  <si>
-    <t>Wargaming</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Futures &amp; Strategy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innovation &amp; Design </t>
-  </si>
-  <si>
-    <t>Software &amp; Automation</t>
-  </si>
-  <si>
-    <t>Fabrication &amp; sUAS</t>
-  </si>
-  <si>
-    <t>Human Performance</t>
-  </si>
-  <si>
-    <t>Policy &amp; Acquisition</t>
-  </si>
-  <si>
-    <t>Community &amp; Workforce.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -367,10 +223,6 @@
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
     </font>
     <font>
       <sz val="11.0"/>
@@ -398,20 +250,14 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="top"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -632,8 +478,6 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="25.38"/>
-    <col customWidth="1" min="5" max="5" width="72.0"/>
-    <col customWidth="1" min="6" max="6" width="150.0"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -649,10 +493,10 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -669,10 +513,10 @@
       <c r="D2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="E2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>10</v>
       </c>
     </row>
@@ -689,16 +533,16 @@
       <c r="D3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -709,16 +553,16 @@
       <c r="D4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>16</v>
+      <c r="E4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
@@ -729,16 +573,16 @@
       <c r="D5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>19</v>
+      <c r="E5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
@@ -749,16 +593,16 @@
       <c r="D6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>22</v>
+      <c r="E6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
@@ -769,16 +613,16 @@
       <c r="D7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>25</v>
+      <c r="E7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
@@ -789,12 +633,16 @@
       <c r="D8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
+      <c r="E8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
@@ -805,12 +653,16 @@
       <c r="D9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
+      <c r="E9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
@@ -821,16 +673,16 @@
       <c r="D10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>30</v>
+      <c r="E10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
@@ -841,16 +693,16 @@
       <c r="D11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>32</v>
+      <c r="E11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
@@ -861,16 +713,16 @@
       <c r="D12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>35</v>
+      <c r="E12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
@@ -881,16 +733,16 @@
       <c r="D13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>37</v>
+      <c r="E13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
@@ -901,601 +753,611 @@
       <c r="D14" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
+      <c r="E14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C15" s="1">
         <v>10.0</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>43</v>
+        <v>31</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C16" s="1">
         <v>1.0</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>46</v>
+        <v>31</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C17" s="1">
         <v>3.0</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>49</v>
+        <v>31</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C18" s="1">
         <v>7.0</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>52</v>
+        <v>31</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C19" s="1">
         <v>2.0</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
+        <v>31</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C20" s="1">
         <v>5.0</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>55</v>
+        <v>31</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C21" s="1">
         <v>6.0</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>58</v>
+        <v>31</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C22" s="1">
         <v>2.0</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>61</v>
+        <v>31</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C23" s="1">
         <v>4.0</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>63</v>
+        <v>31</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="C24" s="1">
         <v>2.0</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>68</v>
+        <v>42</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="C25" s="1">
         <v>5.0</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>71</v>
+        <v>42</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="C26" s="1">
         <v>2.0</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
+        <v>42</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="C27" s="1">
         <v>2.0</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
+        <v>42</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="C28" s="1">
         <v>2.0</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
+        <v>42</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="s">
-        <v>75</v>
+      <c r="A29" s="2" t="s">
+        <v>47</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="C29" s="1">
         <v>2.0</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
+        <v>42</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="s">
-        <v>76</v>
+      <c r="A30" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="C30" s="1">
         <v>2.0</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
+        <v>42</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="C31" s="1">
         <v>2.0</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>79</v>
+        <v>42</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="C32" s="1">
         <v>11.0</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
+        <v>42</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="C33" s="1">
         <v>8.0</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>83</v>
+        <v>42</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>84</v>
+        <v>52</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="C34" s="1">
         <v>6.0</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>86</v>
+        <v>42</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="C35" s="1">
         <v>6.0</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>89</v>
+        <v>42</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>90</v>
+        <v>54</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="C36" s="1">
         <v>6.0</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
+        <v>42</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="s">
-        <v>91</v>
+        <v>55</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="C37" s="1">
         <v>1.0</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E37" s="3"/>
-      <c r="F37" s="3"/>
+        <v>42</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="s">
-        <v>92</v>
+        <v>56</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>93</v>
+        <v>57</v>
       </c>
       <c r="C38" s="1">
         <v>1.0</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="E38" s="3"/>
-      <c r="F38" s="3"/>
+        <v>58</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="s">
-        <v>95</v>
+        <v>59</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>93</v>
+        <v>57</v>
       </c>
       <c r="C39" s="1">
         <v>9.0</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="E39" s="3"/>
-      <c r="F39" s="3"/>
+        <v>58</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>93</v>
+        <v>57</v>
       </c>
       <c r="C40" s="1">
         <v>8.0</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>89</v>
+        <v>58</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="s">
-        <v>98</v>
+        <v>61</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>93</v>
+        <v>57</v>
       </c>
       <c r="C41" s="1">
         <v>6.0</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="E41" s="3"/>
-      <c r="F41" s="3"/>
+        <v>58</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="s">
-        <v>99</v>
+        <v>62</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>93</v>
+        <v>57</v>
       </c>
       <c r="C42" s="1">
         <v>2.0</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="E42" s="3"/>
-      <c r="F42" s="3"/>
+        <v>58</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="s">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>93</v>
+        <v>57</v>
       </c>
       <c r="C43" s="1">
         <v>2.0</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="E43" s="3"/>
-      <c r="F43" s="3"/>
+        <v>58</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>93</v>
+        <v>57</v>
       </c>
       <c r="C44" s="1">
         <v>2.0</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="E47" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="E48" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="E49" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="E50" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="E51" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="E52" s="1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="E53" s="1" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="E54" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="E55" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="E56" s="1" t="s">
-        <v>112</v>
+        <v>58</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/Streamlit.xlsx
+++ b/Streamlit.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="128">
   <si>
     <t>name</t>
   </si>
@@ -94,9 +94,15 @@
     <t>AFGC</t>
   </si>
   <si>
+    <t>Education &amp; PME; AI &amp; Data; Policy &amp; Acquisition</t>
+  </si>
+  <si>
     <t>Blue Horizons</t>
   </si>
   <si>
+    <t>AI &amp; Data; Wargaming; Futures &amp; Strategy; Innovation &amp; Design ; Fabrication &amp; sUAS; Human Performance</t>
+  </si>
+  <si>
     <t>AU HQ</t>
   </si>
   <si>
@@ -130,6 +136,9 @@
     <t>SAASS</t>
   </si>
   <si>
+    <t>Education &amp; PME; Wargaming;  Futures &amp; Strategy</t>
+  </si>
+  <si>
     <t>Auburn</t>
   </si>
   <si>
@@ -157,7 +166,7 @@
     <t>MIT</t>
   </si>
   <si>
-    <t>AI &amp; Data; Education &amp; PME; Innovation &amp; Design</t>
+    <t xml:space="preserve">AI &amp; Data; Education &amp; PME; Innovation &amp; Design; Innovation &amp; Design </t>
   </si>
   <si>
     <t>Supported the Air Power U Summer Workshop Series on AI for research, curriculum, and learning-space design.</t>
@@ -175,6 +184,9 @@
     <t>ASU</t>
   </si>
   <si>
+    <t>Fabrication &amp; sUAS; Education &amp; PME</t>
+  </si>
+  <si>
     <t>Stanford</t>
   </si>
   <si>
@@ -232,15 +244,27 @@
     <t>Aptima</t>
   </si>
   <si>
+    <t>Education &amp; PME; AI &amp; Data; Software &amp; Automation</t>
+  </si>
+  <si>
     <t>Google Public Sector</t>
   </si>
   <si>
+    <t>Education &amp; PME; AI &amp; Data; Innovation &amp; Design; Software &amp; Automation</t>
+  </si>
+  <si>
     <t>Decision Advantage AI</t>
   </si>
   <si>
+    <t>Wargaming; AI &amp; Data</t>
+  </si>
+  <si>
     <t>QuantHub</t>
   </si>
   <si>
+    <t>AI &amp; Data; Education &amp; PME</t>
+  </si>
+  <si>
     <t>Digital University</t>
   </si>
   <si>
@@ -256,6 +280,9 @@
     <t>HII</t>
   </si>
   <si>
+    <t>Innovation &amp; Design; Community &amp; Workforce; Policy &amp; Acquisition</t>
+  </si>
+  <si>
     <t>AWS</t>
   </si>
   <si>
@@ -286,9 +313,15 @@
     <t>SBIR Advisor</t>
   </si>
   <si>
+    <t>Innovation &amp; Design; Education &amp; PME; AI &amp; Data; Fabrication &amp; sUAS</t>
+  </si>
+  <si>
     <t>MGM Chamber of Commerce</t>
   </si>
   <si>
+    <t>Community &amp; Workforce.</t>
+  </si>
+  <si>
     <t>AFRL/RW</t>
   </si>
   <si>
@@ -298,24 +331,39 @@
     <t>Green</t>
   </si>
   <si>
+    <t>AI &amp; Data; Fabrication &amp; sUAS</t>
+  </si>
+  <si>
     <t>Pathfinder/SSG</t>
   </si>
   <si>
+    <t>Innovation &amp; Design; Futures &amp; Strategy</t>
+  </si>
+  <si>
     <t>BESPIN</t>
   </si>
   <si>
-    <t>Software &amp; Automation; Education &amp; PME</t>
+    <t xml:space="preserve">Software &amp; Automation; Education &amp; PME; Software &amp; Automation; Innovation &amp; Design </t>
   </si>
   <si>
     <t>HAF5/7</t>
   </si>
   <si>
+    <t>Education &amp; PME; Wargaming; Innovation &amp; Design;  Futures &amp; Strategy</t>
+  </si>
+  <si>
     <t>103rd Airlift Wing</t>
   </si>
   <si>
+    <t>Innovation &amp; Design; Fabrication &amp; sUAS; Human Performance</t>
+  </si>
+  <si>
     <t>187th Fighter Wing</t>
   </si>
   <si>
+    <t>Innovation &amp; Design; AI &amp; Data</t>
+  </si>
+  <si>
     <t>Army War College</t>
   </si>
   <si>
@@ -347,9 +395,6 @@
   </si>
   <si>
     <t>Policy &amp; Acquisition</t>
-  </si>
-  <si>
-    <t>Community &amp; Workforce.</t>
   </si>
 </sst>
 </file>
@@ -789,12 +834,14 @@
       <c r="D8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="3"/>
+      <c r="E8" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="F8" s="3"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
@@ -805,12 +852,14 @@
       <c r="D9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E9" s="3"/>
+      <c r="E9" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="F9" s="3"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
@@ -822,15 +871,15 @@
         <v>8</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
@@ -845,12 +894,12 @@
         <v>21</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
@@ -862,15 +911,15 @@
         <v>8</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
@@ -885,12 +934,12 @@
         <v>15</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
@@ -901,601 +950,631 @@
       <c r="D14" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3"/>
+      <c r="E14" s="1" t="s">
+        <v>41</v>
+      </c>
       <c r="F14" s="3"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C15" s="1">
         <v>10.0</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C16" s="1">
         <v>1.0</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C17" s="1">
         <v>3.0</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C18" s="1">
         <v>7.0</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C19" s="1">
         <v>2.0</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E19" s="3"/>
+        <v>44</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>57</v>
+      </c>
       <c r="F19" s="3"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C20" s="1">
         <v>5.0</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C21" s="1">
         <v>6.0</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C22" s="1">
         <v>2.0</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C23" s="1">
         <v>4.0</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C24" s="1">
         <v>2.0</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>65</v>
       </c>
       <c r="C25" s="1">
         <v>5.0</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C26" s="1">
         <v>2.0</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E26" s="3"/>
+        <v>70</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>77</v>
+      </c>
       <c r="F26" s="3"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C27" s="1">
         <v>2.0</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E27" s="3"/>
+        <v>70</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>79</v>
+      </c>
       <c r="F27" s="3"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C28" s="1">
         <v>2.0</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E28" s="3"/>
+        <v>70</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>81</v>
+      </c>
       <c r="F28" s="3"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C29" s="1">
         <v>2.0</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E29" s="3"/>
+        <v>70</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>83</v>
+      </c>
       <c r="F29" s="3"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C30" s="1">
         <v>2.0</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E30" s="3"/>
+        <v>70</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>77</v>
+      </c>
       <c r="F30" s="3"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C31" s="1">
         <v>2.0</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C32" s="1">
         <v>11.0</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E32" s="3"/>
+        <v>70</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>89</v>
+      </c>
       <c r="F32" s="3"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C33" s="1">
         <v>8.0</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C34" s="1">
         <v>6.0</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C35" s="1">
         <v>6.0</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C36" s="1">
         <v>6.0</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E36" s="3"/>
+        <v>70</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="F36" s="3"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C37" s="1">
         <v>1.0</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E37" s="3"/>
+        <v>70</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="F37" s="3"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="C38" s="1">
         <v>1.0</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="E38" s="3"/>
+        <v>105</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>106</v>
+      </c>
       <c r="F38" s="3"/>
     </row>
     <row r="39">
       <c r="A39" s="1" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="C39" s="1">
         <v>9.0</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="E39" s="3"/>
+        <v>105</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>108</v>
+      </c>
       <c r="F39" s="3"/>
     </row>
     <row r="40">
       <c r="A40" s="1" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="C40" s="1">
         <v>8.0</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="C41" s="1">
         <v>6.0</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="E41" s="3"/>
+        <v>105</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>112</v>
+      </c>
       <c r="F41" s="3"/>
     </row>
     <row r="42">
       <c r="A42" s="1" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="C42" s="1">
         <v>2.0</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="E42" s="3"/>
+        <v>105</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>114</v>
+      </c>
       <c r="F42" s="3"/>
     </row>
     <row r="43">
       <c r="A43" s="1" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="C43" s="1">
         <v>2.0</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="E43" s="3"/>
+        <v>105</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>116</v>
+      </c>
       <c r="F43" s="3"/>
     </row>
     <row r="44">
       <c r="A44" s="1" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="C44" s="1">
         <v>2.0</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
     </row>
     <row r="47">
       <c r="E47" s="1" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
     </row>
     <row r="48">
       <c r="E48" s="1" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
     </row>
     <row r="49">
       <c r="E49" s="1" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
     </row>
     <row r="50">
       <c r="E50" s="1" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
     </row>
     <row r="51">
       <c r="E51" s="1" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
     </row>
     <row r="52">
       <c r="E52" s="1" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
     </row>
     <row r="53">
       <c r="E53" s="1" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
     </row>
     <row r="54">
       <c r="E54" s="1" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
     </row>
     <row r="55">
       <c r="E55" s="1" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
     </row>
     <row r="56">
       <c r="E56" s="1" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
